--- a/recon-tool/samples/split_B.xlsx
+++ b/recon-tool/samples/split_B.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,191 @@
         <v>40</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PAY-M01</v>
+      </c>
+      <c r="B10" t="str">
+        <v>10/03/2026</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D10">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>PAY-M02</v>
+      </c>
+      <c r="B11" t="str">
+        <v>11/03/2026</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D11">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PAY-M03</v>
+      </c>
+      <c r="B12" t="str">
+        <v>12/03/2026</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D12">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>PAY-M04</v>
+      </c>
+      <c r="B13" t="str">
+        <v>13/03/2026</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D13">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>PAY-M05</v>
+      </c>
+      <c r="B14" t="str">
+        <v>14/03/2026</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D14">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PAY-M06</v>
+      </c>
+      <c r="B15" t="str">
+        <v>15/03/2026</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D15">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PAY-M07</v>
+      </c>
+      <c r="B16" t="str">
+        <v>16/03/2026</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D16">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>PAY-M08</v>
+      </c>
+      <c r="B17" t="str">
+        <v>17/03/2026</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D17">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>PAY-M09</v>
+      </c>
+      <c r="B18" t="str">
+        <v>18/03/2026</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D18">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PAY-M10</v>
+      </c>
+      <c r="B19" t="str">
+        <v>19/03/2026</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D19">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>PAY-M11</v>
+      </c>
+      <c r="B20" t="str">
+        <v>20/03/2026</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D20">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>PAY-M12</v>
+      </c>
+      <c r="B21" t="str">
+        <v>21/03/2026</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D21">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>PAY-M13</v>
+      </c>
+      <c r="B22" t="str">
+        <v>22/03/2026</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D22">
+        <v>1000000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/recon-tool/samples/split_B.xlsx
+++ b/recon-tool/samples/split_B.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -707,9 +707,107 @@
         <v>1000000</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>PAY-DEC</v>
+      </c>
+      <c r="B23" t="str">
+        <v>17/03/2026</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Άσχετη μεγάλη πληρωμή</v>
+      </c>
+      <c r="D23">
+        <v>2557.35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>PAY-K1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>18/03/2026</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Δόση μισθοδοσίας</v>
+      </c>
+      <c r="D24">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>PAY-K2</v>
+      </c>
+      <c r="B25" t="str">
+        <v>19/03/2026</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Δόση μισθοδοσίας</v>
+      </c>
+      <c r="D25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>PAY-K3</v>
+      </c>
+      <c r="B26" t="str">
+        <v>20/03/2026</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Δόση μισθοδοσίας</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PAY-K4</v>
+      </c>
+      <c r="B27" t="str">
+        <v>21/03/2026</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Δόση μισθοδοσίας</v>
+      </c>
+      <c r="D27">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>PAY-K5</v>
+      </c>
+      <c r="B28" t="str">
+        <v>22/03/2026</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Δόση μισθοδοσίας</v>
+      </c>
+      <c r="D28">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>PAY-K6</v>
+      </c>
+      <c r="B29" t="str">
+        <v>23/03/2026</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Υπόλοιπο μισθοδοσίας</v>
+      </c>
+      <c r="D29">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/recon-tool/samples/split_B.xlsx
+++ b/recon-tool/samples/split_B.xlsx
@@ -31,28 +31,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -61,13 +71,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -400,408 +412,408 @@
   <dimension ref="A1:D29"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="2" t="str">
         <v>Αναφορά Πληρωμής</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="2" t="str">
         <v>Ημερομηνία</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" s="2" t="str">
         <v>Περιγραφή</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" s="2" t="str">
         <v>Ποσό</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="2" t="str">
         <v>PAY-01</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" s="2" t="str">
         <v>03/03/2026</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="2" t="str">
         <v>Μερική εξόφληση ΑΛΦΑ</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="2" t="str">
         <v>PAY-02</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="2" t="str">
         <v>08/03/2026</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="2" t="str">
         <v>Μερική εξόφληση ΑΛΦΑ</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>180</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4" s="2" t="str">
         <v>PAY-03</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="2" t="str">
         <v>12/03/2026</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="2" t="str">
         <v>Μερική εξόφληση ΑΛΦΑ</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>120</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5" s="2" t="str">
         <v>PAY-04</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="2" t="str">
         <v>11/03/2026</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="2" t="str">
         <v>Εξόφληση ΓΑΜΑ 1/2</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>150</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6" s="2" t="str">
         <v>PAY-05</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B6" s="2" t="str">
         <v>14/03/2026</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C6" s="2" t="str">
         <v>Εξόφληση ΓΑΜΑ 2/2</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7" s="2" t="str">
         <v>PAY-06</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="2" t="str">
         <v>02/03/2026</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C7" s="2" t="str">
         <v>Λοιπές πληρωμές</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>90</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8" s="2" t="str">
         <v>PAY-07</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B8" s="2" t="str">
         <v>04/03/2026</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C8" s="2" t="str">
         <v>Λοιπές πληρωμές</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>75</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9" s="2" t="str">
         <v>PAY-08</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B9" s="2" t="str">
         <v>06/03/2026</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C9" s="2" t="str">
         <v>Λοιπές πληρωμές</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10" s="2" t="str">
         <v>PAY-M01</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B10" s="2" t="str">
         <v>10/03/2026</v>
       </c>
-      <c r="C10" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D10" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11" s="2" t="str">
         <v>PAY-M02</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11" s="2" t="str">
         <v>11/03/2026</v>
       </c>
-      <c r="C11" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D11" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12" s="2" t="str">
         <v>PAY-M03</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B12" s="2" t="str">
         <v>12/03/2026</v>
       </c>
-      <c r="C12" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D12" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13" s="2" t="str">
         <v>PAY-M04</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B13" s="2" t="str">
         <v>13/03/2026</v>
       </c>
-      <c r="C13" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D13" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14" s="2" t="str">
         <v>PAY-M05</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B14" s="2" t="str">
         <v>14/03/2026</v>
       </c>
-      <c r="C14" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D14" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15" s="2" t="str">
         <v>PAY-M06</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B15" s="2" t="str">
         <v>15/03/2026</v>
       </c>
-      <c r="C15" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D15" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16" s="2" t="str">
         <v>PAY-M07</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B16" s="2" t="str">
         <v>16/03/2026</v>
       </c>
-      <c r="C16" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D16" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
+      <c r="A17" s="2" t="str">
         <v>PAY-M08</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B17" s="2" t="str">
         <v>17/03/2026</v>
       </c>
-      <c r="C17" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D17" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18" s="2" t="str">
         <v>PAY-M09</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B18" s="2" t="str">
         <v>18/03/2026</v>
       </c>
-      <c r="C18" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D18" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
+      <c r="A19" s="2" t="str">
         <v>PAY-M10</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B19" s="2" t="str">
         <v>19/03/2026</v>
       </c>
-      <c r="C19" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D19" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
+      <c r="A20" s="2" t="str">
         <v>PAY-M11</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B20" s="2" t="str">
         <v>20/03/2026</v>
       </c>
-      <c r="C20" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D20" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
+      <c r="A21" s="2" t="str">
         <v>PAY-M12</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B21" s="2" t="str">
         <v>21/03/2026</v>
       </c>
-      <c r="C21" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D21" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
+      <c r="A22" s="2" t="str">
         <v>PAY-M13</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B22" s="2" t="str">
         <v>22/03/2026</v>
       </c>
-      <c r="C22" t="str">
-        <v>Δόση μεταφοράς</v>
-      </c>
-      <c r="D22">
+      <c r="C22" s="2" t="str">
+        <v>Δόση μεταφοράς</v>
+      </c>
+      <c r="D22" s="2">
         <v>1000000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23" s="2" t="str">
         <v>PAY-DEC</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B23" s="2" t="str">
         <v>17/03/2026</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C23" s="2" t="str">
         <v>Άσχετη μεγάλη πληρωμή</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>2557.35</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
+      <c r="A24" s="2" t="str">
         <v>PAY-K1</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B24" s="2" t="str">
         <v>18/03/2026</v>
       </c>
-      <c r="C24" t="str">
+      <c r="C24" s="2" t="str">
         <v>Δόση μισθοδοσίας</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
+      <c r="A25" s="2" t="str">
         <v>PAY-K2</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B25" s="2" t="str">
         <v>19/03/2026</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C25" s="2" t="str">
         <v>Δόση μισθοδοσίας</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
+      <c r="A26" s="2" t="str">
         <v>PAY-K3</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B26" s="2" t="str">
         <v>20/03/2026</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C26" s="2" t="str">
         <v>Δόση μισθοδοσίας</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
+      <c r="A27" s="2" t="str">
         <v>PAY-K4</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B27" s="2" t="str">
         <v>21/03/2026</v>
       </c>
-      <c r="C27" t="str">
+      <c r="C27" s="2" t="str">
         <v>Δόση μισθοδοσίας</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
+      <c r="A28" s="2" t="str">
         <v>PAY-K5</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B28" s="2" t="str">
         <v>22/03/2026</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C28" s="2" t="str">
         <v>Δόση μισθοδοσίας</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
+      <c r="A29" s="2" t="str">
         <v>PAY-K6</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B29" s="2" t="str">
         <v>23/03/2026</v>
       </c>
-      <c r="C29" t="str">
+      <c r="C29" s="2" t="str">
         <v>Υπόλοιπο μισθοδοσίας</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>500</v>
       </c>
     </row>
